--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C2EE93-92D8-A044-97CF-5025349BB51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1260397-91F4-594C-B7E6-35AE06414143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="44">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -99,6 +99,75 @@
   </si>
   <si>
     <t>0.5733284681</t>
+  </si>
+  <si>
+    <t>0.0626436782</t>
+  </si>
+  <si>
+    <t>0.0028735632</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.5243225384</t>
+  </si>
+  <si>
+    <t>0.0844827586</t>
+  </si>
+  <si>
+    <t>0.0074712643</t>
+  </si>
+  <si>
+    <t>0.5522972616</t>
+  </si>
+  <si>
+    <t>LESS NODES, MORE EDGES</t>
+  </si>
+  <si>
+    <t>MORE NODES, LESS EDGES</t>
+  </si>
+  <si>
+    <t>SAME AS ONLY TEXT</t>
+  </si>
+  <si>
+    <t>SAME AS TEXT + CLAIM</t>
+  </si>
+  <si>
+    <t>0.0007662835</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>0.4154562962</t>
+  </si>
+  <si>
+    <t>text + node speaker</t>
+  </si>
+  <si>
+    <t>MODEL'S TYPE</t>
+  </si>
+  <si>
+    <t>Transactional</t>
+  </si>
+  <si>
+    <t>Semantic Matching</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>text + node claim/premise</t>
+  </si>
+  <si>
+    <t>text + node year</t>
+  </si>
+  <si>
+    <t>MORE CONNECTED NODES</t>
+  </si>
+  <si>
+    <t>MORE NODES, MORE CONNECTED, LESS THAN USING NODE CLAIM/PREMISE</t>
+  </si>
+  <si>
+    <t>MORE CONNECTED NODES, LESS THAN NODE CLAIM/PREMISE</t>
   </si>
 </sst>
 </file>
@@ -122,7 +191,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,6 +201,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -148,12 +229,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -470,152 +560,421 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D0B245-65CB-DF4D-8DE7-CF9F5E969E09}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" style="2"/>
-    <col min="2" max="2" width="37.33203125" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="21.33203125" style="2"/>
+    <col min="1" max="2" width="21.33203125" style="2"/>
+    <col min="3" max="3" width="37.33203125" style="2" customWidth="1"/>
+    <col min="4" max="6" width="21.33203125" style="2"/>
+    <col min="7" max="8" width="11" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="21.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G8" s="3"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I14" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1260397-91F4-594C-B7E6-35AE06414143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5087EF-0EE7-1D4B-861B-F28206370832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="-51200" yWindow="-9160" windowWidth="51200" windowHeight="28800" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -168,6 +168,33 @@
   </si>
   <si>
     <t>MORE CONNECTED NODES, LESS THAN NODE CLAIM/PREMISE</t>
+  </si>
+  <si>
+    <t>0.2962933629</t>
+  </si>
+  <si>
+    <t>0.2755425313</t>
+  </si>
+  <si>
+    <t>0.540100494</t>
+  </si>
+  <si>
+    <t>0.0773800095</t>
+  </si>
+  <si>
+    <t>0.0139394899</t>
+  </si>
+  <si>
+    <t>0.4006781798</t>
+  </si>
+  <si>
+    <t>0.2936797085</t>
+  </si>
+  <si>
+    <t>0.2936005068</t>
+  </si>
+  <si>
+    <t>0.7101192774</t>
   </si>
 </sst>
 </file>
@@ -206,13 +233,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -229,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -238,6 +265,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -560,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D0B245-65CB-DF4D-8DE7-CF9F5E969E09}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.33203125" style="2"/>
@@ -595,7 +625,7 @@
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -658,7 +688,7 @@
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -790,7 +820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>36</v>
@@ -801,6 +831,15 @@
       <c r="C22" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="D22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="I22" s="2" t="s">
         <v>41</v>
       </c>
@@ -815,18 +854,34 @@
       <c r="C23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="D23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -905,78 +960,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
+    <row r="34" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5087EF-0EE7-1D4B-861B-F28206370832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AE2416-2DA2-3345-8B1D-97B277CF11CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-9160" windowWidth="51200" windowHeight="28800" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="59">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -195,6 +195,24 @@
   </si>
   <si>
     <t>0.7101192774</t>
+  </si>
+  <si>
+    <t>0.3904547813</t>
+  </si>
+  <si>
+    <t>0.1872730417</t>
+  </si>
+  <si>
+    <t>0.8820455872</t>
+  </si>
+  <si>
+    <t>0.274165658</t>
+  </si>
+  <si>
+    <t>0.8009771642</t>
+  </si>
+  <si>
+    <t>0.0012104444</t>
   </si>
 </sst>
 </file>
@@ -256,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -265,9 +283,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -625,7 +640,7 @@
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -688,7 +703,7 @@
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -820,7 +835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>36</v>
@@ -854,10 +869,10 @@
       <c r="C23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -868,7 +883,7 @@
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -894,6 +909,15 @@
       <c r="C26" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="D26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="I26" s="2" t="s">
         <v>42</v>
       </c>
@@ -908,6 +932,15 @@
       <c r="C27" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="D27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
@@ -960,7 +993,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" s="5" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AE2416-2DA2-3345-8B1D-97B277CF11CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D5367B-27BB-AD44-A1DC-AEA9CDF02BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="66">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -213,6 +213,27 @@
   </si>
   <si>
     <t>0.0012104444</t>
+  </si>
+  <si>
+    <t>0.0089918727</t>
+  </si>
+  <si>
+    <t>0.0745287913</t>
+  </si>
+  <si>
+    <t>0.6604284674</t>
+  </si>
+  <si>
+    <t>text + node speaker + node year</t>
+  </si>
+  <si>
+    <t>text + node claim/premise + node  year</t>
+  </si>
+  <si>
+    <t>text + node claim/premise + node speaker</t>
+  </si>
+  <si>
+    <t>text + all</t>
   </si>
 </sst>
 </file>
@@ -605,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D0B245-65CB-DF4D-8DE7-CF9F5E969E09}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.33203125" style="2"/>
@@ -903,19 +924,19 @@
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -952,6 +973,15 @@
       <c r="C28" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="D28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F29" s="3"/>
@@ -993,7 +1023,138 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D5367B-27BB-AD44-A1DC-AEA9CDF02BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7233F772-ABE0-104D-8E51-7F6041E7D158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="3540" yWindow="760" windowWidth="26700" windowHeight="17360" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -234,6 +234,84 @@
   </si>
   <si>
     <t>text + all</t>
+  </si>
+  <si>
+    <t>0.490628347</t>
+  </si>
+  <si>
+    <t>0.0072295609</t>
+  </si>
+  <si>
+    <t>0.8961679104</t>
+  </si>
+  <si>
+    <t>0.4732238486</t>
+  </si>
+  <si>
+    <t>0.011513745</t>
+  </si>
+  <si>
+    <t>0.834346166</t>
+  </si>
+  <si>
+    <t>0.0828275616</t>
+  </si>
+  <si>
+    <t>0.227418779</t>
+  </si>
+  <si>
+    <t>0.5127159227</t>
+  </si>
+  <si>
+    <t>0.4226755218</t>
+  </si>
+  <si>
+    <t>0.2268079275</t>
+  </si>
+  <si>
+    <t>0.7751963901</t>
+  </si>
+  <si>
+    <t>0.1771558086</t>
+  </si>
+  <si>
+    <t>0.0010014759</t>
+  </si>
+  <si>
+    <t>0.6505134162</t>
+  </si>
+  <si>
+    <t>political1</t>
+  </si>
+  <si>
+    <t>political</t>
+  </si>
+  <si>
+    <t>0.0025300443</t>
+  </si>
+  <si>
+    <t>0.1602888467</t>
+  </si>
+  <si>
+    <t>0.4896978934</t>
+  </si>
+  <si>
+    <t>0.2936055884</t>
+  </si>
+  <si>
+    <t>0.0154755508</t>
+  </si>
+  <si>
+    <t>0.7350155096</t>
+  </si>
+  <si>
+    <t>0.4144008598</t>
+  </si>
+  <si>
+    <t>0.2414830736</t>
+  </si>
+  <si>
+    <t>0.9011992188</t>
   </si>
 </sst>
 </file>
@@ -991,11 +1069,20 @@
       <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>40</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>43</v>
@@ -1011,6 +1098,15 @@
       <c r="C31" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="D31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
@@ -1022,19 +1118,40 @@
       <c r="C32" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>5</v>
+      <c r="B34" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
@@ -1044,19 +1161,37 @@
       <c r="C35" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
@@ -1066,8 +1201,20 @@
       <c r="C38" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>37</v>
       </c>
@@ -1077,8 +1224,17 @@
       <c r="C39" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -1089,7 +1245,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
@@ -1100,7 +1256,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>37</v>
       </c>
@@ -1111,7 +1267,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>38</v>
       </c>
@@ -1122,7 +1278,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>36</v>
       </c>
@@ -1133,7 +1289,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>37</v>
       </c>
@@ -1144,7 +1300,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7233F772-ABE0-104D-8E51-7F6041E7D158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC639A5-42D4-164C-AAE5-7C852895A177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="760" windowWidth="26700" windowHeight="17360" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="4280" yWindow="760" windowWidth="26700" windowHeight="17360" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="95">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -312,6 +312,15 @@
   </si>
   <si>
     <t>0.9011992188</t>
+  </si>
+  <si>
+    <t>0.1947877485</t>
+  </si>
+  <si>
+    <t>0.196399785</t>
+  </si>
+  <si>
+    <t>0.4499270134</t>
   </si>
 </sst>
 </file>
@@ -1201,13 +1210,13 @@
       <c r="C38" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="3" t="s">
         <v>91</v>
       </c>
       <c r="I38" s="2" t="s">
@@ -1243,6 +1252,15 @@
       </c>
       <c r="C40" s="2" t="s">
         <v>63</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC639A5-42D4-164C-AAE5-7C852895A177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6302BB43-0F82-CB4D-A010-AD7B09C68234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4280" yWindow="760" windowWidth="26700" windowHeight="17360" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="98">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -321,6 +321,15 @@
   </si>
   <si>
     <t>0.4499270134</t>
+  </si>
+  <si>
+    <t>0.3357264957</t>
+  </si>
+  <si>
+    <t>0.234017094</t>
+  </si>
+  <si>
+    <t>0.9333471727</t>
   </si>
 </sst>
 </file>
@@ -1273,6 +1282,15 @@
       <c r="C42" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="D42" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6302BB43-0F82-CB4D-A010-AD7B09C68234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E86D7A-4D80-8447-8ECB-949BB042790B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="760" windowWidth="26700" windowHeight="17360" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="130">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -119,18 +119,6 @@
     <t>0.5522972616</t>
   </si>
   <si>
-    <t>LESS NODES, MORE EDGES</t>
-  </si>
-  <si>
-    <t>MORE NODES, LESS EDGES</t>
-  </si>
-  <si>
-    <t>SAME AS ONLY TEXT</t>
-  </si>
-  <si>
-    <t>SAME AS TEXT + CLAIM</t>
-  </si>
-  <si>
     <t>0.0007662835</t>
   </si>
   <si>
@@ -161,15 +149,6 @@
     <t>text + node year</t>
   </si>
   <si>
-    <t>MORE CONNECTED NODES</t>
-  </si>
-  <si>
-    <t>MORE NODES, MORE CONNECTED, LESS THAN USING NODE CLAIM/PREMISE</t>
-  </si>
-  <si>
-    <t>MORE CONNECTED NODES, LESS THAN NODE CLAIM/PREMISE</t>
-  </si>
-  <si>
     <t>0.2962933629</t>
   </si>
   <si>
@@ -233,9 +212,6 @@
     <t>text + node claim/premise + node speaker</t>
   </si>
   <si>
-    <t>text + all</t>
-  </si>
-  <si>
     <t>0.490628347</t>
   </si>
   <si>
@@ -281,12 +257,6 @@
     <t>0.6505134162</t>
   </si>
   <si>
-    <t>political1</t>
-  </si>
-  <si>
-    <t>political</t>
-  </si>
-  <si>
     <t>0.0025300443</t>
   </si>
   <si>
@@ -330,13 +300,139 @@
   </si>
   <si>
     <t>0.9333471727</t>
+  </si>
+  <si>
+    <t>0.0298005698</t>
+  </si>
+  <si>
+    <t>0.3485470085</t>
+  </si>
+  <si>
+    <t>0.693725746</t>
+  </si>
+  <si>
+    <t>0.4997720798</t>
+  </si>
+  <si>
+    <t>0.1336752137</t>
+  </si>
+  <si>
+    <t>0.9321209359</t>
+  </si>
+  <si>
+    <t>NODE EXAMPLE</t>
+  </si>
+  <si>
+    <t>RELATION EXAMPLE</t>
+  </si>
+  <si>
+    <t>support, attack, equivalent</t>
+  </si>
+  <si>
+    <t>text - speaker_name</t>
+  </si>
+  <si>
+    <t>text - claim /premise</t>
+  </si>
+  <si>
+    <t>every text has only one speaker so adding the speaker won't affect the graph by adding nodes or relations, same as using only text</t>
+  </si>
+  <si>
+    <t>every text has only one speaker so adding the speaker won't affect the graph by adding nodes or relations, same as using  text + claim/premise</t>
+  </si>
+  <si>
+    <t>Using only text, without considering if the nodes are claim or premises</t>
+  </si>
+  <si>
+    <t>by using the claim/premise we increase tjhe number of nodes and relations because for each text is possibile to create two different nodes with different connections</t>
+  </si>
+  <si>
+    <t>text - claim /premise - speaker_name</t>
+  </si>
+  <si>
+    <t>text; claim/premise;</t>
+  </si>
+  <si>
+    <t>support, attack, equivalent, is_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in this setting we have 3 types of nodes: "text" and "claim" and "premise". The node "claim" and "premises" are connected to every other node with the relation "is a". Therefore we significantly increase the number of edges </t>
+  </si>
+  <si>
+    <t>support, attack, equivalent, spoken by, role</t>
+  </si>
+  <si>
+    <t>text; speaker; role;</t>
+  </si>
+  <si>
+    <t>text; year</t>
+  </si>
+  <si>
+    <t>support, attack, equivalent, debate's year</t>
+  </si>
+  <si>
+    <t>we have 2 types of nodes: "text" and "year". Each text is connected to a node year with the relation "debates's year"</t>
+  </si>
+  <si>
+    <t>3 types of nodes: "text", "speaker name" and "role". Each node speaker is connected to the nodes "text" by the relation "spoken by". Each node speaker is also connected to the node "role" by the relation "role". Nodes role can be: president, vice-president, president candidate, vice-president candidate. We increased the number of edges, added more nodes and more informations</t>
+  </si>
+  <si>
+    <t>support, attack, equivalent, is a, debates's year</t>
+  </si>
+  <si>
+    <t>text; claim/premise; year</t>
+  </si>
+  <si>
+    <t>support, attack, equivalent, is_a, spoken_by</t>
+  </si>
+  <si>
+    <t>text; claim/premise; speaker_name; role</t>
+  </si>
+  <si>
+    <t>support, attack, queivalent, spoken_by, role, debate's year</t>
+  </si>
+  <si>
+    <t>support, attack, is_a, equivalent, spoken_by, role, debate's year</t>
+  </si>
+  <si>
+    <t>text + claim/premise + node speaker</t>
+  </si>
+  <si>
+    <t>text + claim/premise + node year</t>
+  </si>
+  <si>
+    <t>text + node claim/premise, year, speaker</t>
+  </si>
+  <si>
+    <t>text + claim/premise + node year, speaker</t>
+  </si>
+  <si>
+    <t>support, attack, equivalent, spoken_by, role</t>
+  </si>
+  <si>
+    <t>text - claim/premise; speaker_name, role</t>
+  </si>
+  <si>
+    <t>text; claim/premise; speaker_name; role; debate's year</t>
+  </si>
+  <si>
+    <t>text; speaker_name; role; debate's year</t>
+  </si>
+  <si>
+    <t>text + claim/premise; year</t>
+  </si>
+  <si>
+    <t>text + claim/premise; speaker_name; role; year</t>
+  </si>
+  <si>
+    <t>support, attack, equivalent, spoken_by, role, debate's year</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -352,8 +448,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,18 +484,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,22 +500,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -722,20 +852,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D0B245-65CB-DF4D-8DE7-CF9F5E969E09}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="21.33203125" style="2"/>
-    <col min="3" max="3" width="37.33203125" style="2" customWidth="1"/>
-    <col min="4" max="6" width="21.33203125" style="2"/>
-    <col min="7" max="8" width="11" style="2" customWidth="1"/>
-    <col min="9" max="9" width="28.6640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="21.33203125" style="2"/>
+    <col min="1" max="1" width="22.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="40.5" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="48.1640625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="59.6640625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="85.5" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="21.33203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -752,602 +886,1016 @@
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>36</v>
+      <c r="A2" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="E4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F10" s="6"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="C24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="H25" s="11"/>
+    </row>
+    <row r="27" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="B27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="12"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="B28" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E35" s="6"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C42" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C44" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E50" s="6"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C52" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C53" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C54" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C57" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="C58" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B59" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="5" t="s">
+      <c r="C59" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C62" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="B64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C67" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="B68" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>65</v>
+      <c r="C68" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="I27:J29"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="I2:I4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E86D7A-4D80-8447-8ECB-949BB042790B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6355A0-8116-DF47-887E-76E6858CF75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -500,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -514,19 +514,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -537,6 +528,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -856,14 +850,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="40.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="19.6640625" style="4" customWidth="1"/>
     <col min="6" max="6" width="19.1640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="48.1640625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="59.6640625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="85.5" style="10" customWidth="1"/>
+    <col min="7" max="7" width="48.1640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="59.6640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="85.5" style="7" customWidth="1"/>
     <col min="10" max="16384" width="21.33203125" style="4"/>
   </cols>
   <sheetData>
@@ -904,22 +898,22 @@
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>101</v>
       </c>
     </row>
@@ -927,7 +921,7 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -942,19 +936,19 @@
       <c r="F3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="8"/>
+      <c r="I3" s="10"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -969,13 +963,13 @@
       <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="8"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -987,22 +981,22 @@
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="10" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1010,7 +1004,7 @@
       <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1025,19 +1019,19 @@
       <c r="F8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="8"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -1049,19 +1043,19 @@
       <c r="E9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="8"/>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F10" s="6"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
@@ -1073,13 +1067,13 @@
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="10" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1087,37 +1081,37 @@
       <c r="A13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="8"/>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="8"/>
+      <c r="I14" s="10"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
@@ -1129,13 +1123,13 @@
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="10" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1143,53 +1137,53 @@
       <c r="A18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="8"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="8"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -1198,13 +1192,13 @@
       <c r="F22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="10" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1212,7 +1206,7 @@
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1227,19 +1221,19 @@
       <c r="F23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="8"/>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -1248,61 +1242,61 @@
       <c r="D24" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="8"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="H25" s="11"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="27" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="12"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -1317,21 +1311,21 @@
       <c r="F28" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="12"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -1346,45 +1340,45 @@
       <c r="F29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="12"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="9"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F31" s="6"/>
+      <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="10" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1392,7 +1386,7 @@
       <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -1407,19 +1401,19 @@
       <c r="F33" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I33" s="8"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -1428,46 +1422,46 @@
       <c r="D34" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="5" t="s">
         <v>65</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I34" s="8"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E35" s="6"/>
+      <c r="E35" s="5"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="6" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1475,7 +1469,7 @@
       <c r="A38" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -1490,10 +1484,10 @@
       <c r="F38" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="6" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1501,7 +1495,7 @@
       <c r="A39" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -1516,10 +1510,10 @@
       <c r="F39" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="6" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1527,25 +1521,25 @@
       <c r="A42" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="6" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1553,7 +1547,7 @@
       <c r="A43" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -1568,10 +1562,10 @@
       <c r="F43" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="6" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1579,7 +1573,7 @@
       <c r="A44" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -1594,10 +1588,10 @@
       <c r="F44" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="6" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1605,7 +1599,7 @@
       <c r="A47" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -1617,13 +1611,13 @@
       <c r="E47" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="H47" s="6" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1631,13 +1625,13 @@
       <c r="A48" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>91</v>
       </c>
       <c r="E48" s="4" t="s">
@@ -1646,10 +1640,10 @@
       <c r="F48" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="6" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1657,7 +1651,7 @@
       <c r="A49" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -1666,36 +1660,36 @@
       <c r="D49" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="5" t="s">
         <v>89</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="H49" s="6" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E50" s="6"/>
+      <c r="E50" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="6" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1703,16 +1697,16 @@
       <c r="A53" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="H53" s="6" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1720,16 +1714,16 @@
       <c r="A54" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="H54" s="7" t="s">
+      <c r="H54" s="6" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1737,16 +1731,16 @@
       <c r="A57" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G57" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="H57" s="6" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1754,16 +1748,16 @@
       <c r="A58" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G58" s="7" t="s">
+      <c r="G58" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="H58" s="6" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1771,16 +1765,16 @@
       <c r="A59" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G59" s="7" t="s">
+      <c r="G59" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H59" s="7" t="s">
+      <c r="H59" s="6" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1788,16 +1782,16 @@
       <c r="A62" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G62" s="7" t="s">
+      <c r="G62" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H62" s="7" t="s">
+      <c r="H62" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1805,16 +1799,16 @@
       <c r="A63" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H63" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1822,16 +1816,16 @@
       <c r="A64" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="H64" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1839,16 +1833,16 @@
       <c r="A66" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G66" s="7" t="s">
+      <c r="G66" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="H66" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1856,16 +1850,16 @@
       <c r="A67" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="H67" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1873,28 +1867,28 @@
       <c r="A68" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="G68" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H68" s="7" t="s">
+      <c r="H68" s="6" t="s">
         <v>129</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="I2:I4"/>
     <mergeCell ref="I32:I34"/>
     <mergeCell ref="I27:J29"/>
     <mergeCell ref="I22:I24"/>
     <mergeCell ref="I17:I19"/>
     <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="I2:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6355A0-8116-DF47-887E-76E6858CF75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6337571E-F1D1-4D44-8F2A-A280269B13F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="161">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -426,6 +426,99 @@
   </si>
   <si>
     <t>support, attack, equivalent, spoken_by, role, debate's year</t>
+  </si>
+  <si>
+    <t>0.2580059946</t>
+  </si>
+  <si>
+    <t>0.2438870485</t>
+  </si>
+  <si>
+    <t>0.8587045372</t>
+  </si>
+  <si>
+    <t>0.3375138034</t>
+  </si>
+  <si>
+    <t>0.8019814977</t>
+  </si>
+  <si>
+    <t>0.4637052233</t>
+  </si>
+  <si>
+    <t>0.0357424649</t>
+  </si>
+  <si>
+    <t>0.88583775</t>
+  </si>
+  <si>
+    <t>0.4701751617</t>
+  </si>
+  <si>
+    <t>0.8857051387</t>
+  </si>
+  <si>
+    <t>0.3950152268</t>
+  </si>
+  <si>
+    <t>0.1832425068</t>
+  </si>
+  <si>
+    <t>0.7897418397</t>
+  </si>
+  <si>
+    <t>0.0532418363</t>
+  </si>
+  <si>
+    <t>0.2982331598</t>
+  </si>
+  <si>
+    <t>0.6187357919</t>
+  </si>
+  <si>
+    <t>0.000298033</t>
+  </si>
+  <si>
+    <t>0.0007450824</t>
+  </si>
+  <si>
+    <t>0.5056448533</t>
+  </si>
+  <si>
+    <t>0.3606199086</t>
+  </si>
+  <si>
+    <t>0.0328829723</t>
+  </si>
+  <si>
+    <t>0.9014450974</t>
+  </si>
+  <si>
+    <t>0.603169084</t>
+  </si>
+  <si>
+    <t>0.0121696801</t>
+  </si>
+  <si>
+    <t>0.9519743861</t>
+  </si>
+  <si>
+    <t>0.2615803815</t>
+  </si>
+  <si>
+    <t>0.0105786184</t>
+  </si>
+  <si>
+    <t>0.7922069938</t>
+  </si>
+  <si>
+    <t>0.0004734101</t>
+  </si>
+  <si>
+    <t>0.0001578034</t>
+  </si>
+  <si>
+    <t>0.2819831953</t>
   </si>
 </sst>
 </file>
@@ -474,7 +567,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,6 +577,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -529,8 +628,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -852,9 +987,9 @@
     <col min="1" max="1" width="22.5" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="40.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" style="15" customWidth="1"/>
     <col min="7" max="7" width="48.1640625" style="6" customWidth="1"/>
     <col min="8" max="8" width="59.6640625" style="6" customWidth="1"/>
     <col min="9" max="9" width="85.5" style="7" customWidth="1"/>
@@ -871,13 +1006,13 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -898,13 +1033,13 @@
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="14" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -913,7 +1048,7 @@
       <c r="H2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="17" t="s">
         <v>101</v>
       </c>
     </row>
@@ -927,13 +1062,13 @@
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -942,7 +1077,7 @@
       <c r="H3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="10"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -954,13 +1089,13 @@
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -969,7 +1104,7 @@
       <c r="H4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="10"/>
+      <c r="I4" s="17"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -981,13 +1116,13 @@
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="6" t="s">
@@ -996,7 +1131,7 @@
       <c r="H7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="17" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1010,13 +1145,13 @@
       <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -1025,7 +1160,7 @@
       <c r="H8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
@@ -1037,13 +1172,13 @@
       <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1052,10 +1187,10 @@
       <c r="H9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="10"/>
+      <c r="I9" s="17"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F10" s="5"/>
+      <c r="F10" s="14"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
@@ -1073,7 +1208,7 @@
       <c r="H12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="17" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1093,7 +1228,7 @@
       <c r="H13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="10"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
@@ -1111,7 +1246,7 @@
       <c r="H14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
@@ -1129,7 +1264,7 @@
       <c r="H17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="17" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1149,7 +1284,7 @@
       <c r="H18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
@@ -1167,7 +1302,7 @@
       <c r="H19" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="10"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G20" s="8"/>
@@ -1183,13 +1318,13 @@
       <c r="C22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="15" t="s">
         <v>39</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -1198,7 +1333,7 @@
       <c r="H22" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="17" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1212,13 +1347,13 @@
       <c r="C23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="15" t="s">
         <v>42</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -1227,7 +1362,7 @@
       <c r="H23" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="10"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
@@ -1239,13 +1374,13 @@
       <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="14" t="s">
         <v>45</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -1254,11 +1389,11 @@
       <c r="H24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="10"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
       <c r="H25" s="8"/>
     </row>
     <row r="27" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1271,13 +1406,13 @@
       <c r="C27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="14" t="s">
         <v>48</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -1286,10 +1421,10 @@
       <c r="H27" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="J27" s="10"/>
+      <c r="J27" s="17"/>
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -1302,13 +1437,13 @@
       <c r="C28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="15" t="s">
         <v>50</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -1317,8 +1452,8 @@
       <c r="H28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -1331,13 +1466,13 @@
       <c r="C29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="15" t="s">
         <v>54</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -1346,12 +1481,12 @@
       <c r="H29" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
       <c r="K29" s="9"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F31" s="5"/>
+      <c r="F31" s="14"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
@@ -1363,13 +1498,13 @@
       <c r="C32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="14" t="s">
         <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
@@ -1378,7 +1513,7 @@
       <c r="H32" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="17" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1392,13 +1527,13 @@
       <c r="C33" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G33" s="6" t="s">
@@ -1407,7 +1542,7 @@
       <c r="H33" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I33" s="10"/>
+      <c r="I33" s="17"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
@@ -1419,13 +1554,13 @@
       <c r="C34" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="15" t="s">
         <v>66</v>
       </c>
       <c r="G34" s="6" t="s">
@@ -1434,10 +1569,10 @@
       <c r="H34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I34" s="10"/>
+      <c r="I34" s="17"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E35" s="5"/>
+      <c r="E35" s="14"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
@@ -1449,13 +1584,13 @@
       <c r="C37" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="14" t="s">
         <v>69</v>
       </c>
       <c r="G37" s="6" t="s">
@@ -1475,13 +1610,13 @@
       <c r="C38" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="G38" s="6" t="s">
@@ -1501,13 +1636,13 @@
       <c r="C39" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G39" s="6" t="s">
@@ -1527,13 +1662,13 @@
       <c r="C42" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="14" t="s">
         <v>81</v>
       </c>
       <c r="G42" s="6" t="s">
@@ -1553,13 +1688,13 @@
       <c r="C43" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="15" t="s">
         <v>78</v>
       </c>
       <c r="G43" s="6" t="s">
@@ -1579,13 +1714,13 @@
       <c r="C44" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="15" t="s">
         <v>84</v>
       </c>
       <c r="G44" s="6" t="s">
@@ -1605,13 +1740,13 @@
       <c r="C47" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="14" t="s">
         <v>87</v>
       </c>
       <c r="G47" s="6" t="s">
@@ -1631,13 +1766,13 @@
       <c r="C48" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="15" t="s">
         <v>93</v>
       </c>
       <c r="G48" s="6" t="s">
@@ -1647,7 +1782,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>34</v>
       </c>
@@ -1657,13 +1792,13 @@
       <c r="C49" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="15" t="s">
         <v>90</v>
       </c>
       <c r="G49" s="6" t="s">
@@ -1673,10 +1808,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E50" s="5"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E50" s="14"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>32</v>
       </c>
@@ -1686,6 +1821,15 @@
       <c r="C52" s="4" t="s">
         <v>121</v>
       </c>
+      <c r="D52" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>142</v>
+      </c>
       <c r="G52" s="6" t="s">
         <v>125</v>
       </c>
@@ -1693,7 +1837,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>33</v>
       </c>
@@ -1703,6 +1847,15 @@
       <c r="C53" s="4" t="s">
         <v>121</v>
       </c>
+      <c r="D53" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>157</v>
+      </c>
       <c r="G53" s="6" t="s">
         <v>125</v>
       </c>
@@ -1710,24 +1863,28 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
+    <row r="54" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H54" s="11" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54" s="12"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>32</v>
       </c>
@@ -1737,6 +1894,15 @@
       <c r="C57" s="4" t="s">
         <v>119</v>
       </c>
+      <c r="D57" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>132</v>
+      </c>
       <c r="G57" s="6" t="s">
         <v>124</v>
       </c>
@@ -1744,7 +1910,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>33</v>
       </c>
@@ -1754,6 +1920,15 @@
       <c r="C58" s="4" t="s">
         <v>119</v>
       </c>
+      <c r="D58" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>134</v>
+      </c>
       <c r="G58" s="6" t="s">
         <v>124</v>
       </c>
@@ -1761,24 +1936,34 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
+    <row r="59" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="D59" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="G59" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="H59" s="6" t="s">
+      <c r="H59" s="20" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I59" s="21"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>32</v>
       </c>
@@ -1788,6 +1973,15 @@
       <c r="C62" s="4" t="s">
         <v>120</v>
       </c>
+      <c r="D62" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>137</v>
+      </c>
       <c r="G62" s="6" t="s">
         <v>127</v>
       </c>
@@ -1795,7 +1989,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>33</v>
       </c>
@@ -1805,6 +1999,15 @@
       <c r="C63" s="4" t="s">
         <v>120</v>
       </c>
+      <c r="D63" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>139</v>
+      </c>
       <c r="G63" s="6" t="s">
         <v>127</v>
       </c>
@@ -1812,24 +2015,34 @@
         <v>110</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
+    <row r="64" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="D64" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="H64" s="20" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I64" s="21"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>32</v>
       </c>
@@ -1839,6 +2052,15 @@
       <c r="C66" s="4" t="s">
         <v>122</v>
       </c>
+      <c r="D66" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>154</v>
+      </c>
       <c r="G66" s="6" t="s">
         <v>128</v>
       </c>
@@ -1846,7 +2068,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>33</v>
       </c>
@@ -1856,6 +2078,15 @@
       <c r="C67" s="4" t="s">
         <v>122</v>
       </c>
+      <c r="D67" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>151</v>
+      </c>
       <c r="G67" s="6" t="s">
         <v>128</v>
       </c>
@@ -1863,22 +2094,32 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
+    <row r="68" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="D68" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G68" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="H68" s="6" t="s">
+      <c r="H68" s="20" t="s">
         <v>129</v>
       </c>
+      <c r="I68" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1890,6 +2131,66 @@
     <mergeCell ref="I17:I19"/>
     <mergeCell ref="I12:I14"/>
   </mergeCells>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F4">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F1048576">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6337571E-F1D1-4D44-8F2A-A280269B13F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF923DE-FBDB-2943-875E-647209FABC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="167">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -519,13 +520,31 @@
   </si>
   <si>
     <t>0.2819831953</t>
+  </si>
+  <si>
+    <t>FILTRI</t>
+  </si>
+  <si>
+    <t>F1 MACRO &gt; 70</t>
+  </si>
+  <si>
+    <t>ConvE: tanti nodi tutti connessi; TransE does better in all, DistMult every node but not so connected</t>
+  </si>
+  <si>
+    <t>STABILITY</t>
+  </si>
+  <si>
+    <t>HITS@10 LP, HITS@10 LP &gt; 0.1</t>
+  </si>
+  <si>
+    <t>NOT MORE THAN 0.20 DIFFERENCE BETWEEN LD AND LD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -566,8 +585,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -582,7 +609,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFBED7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -628,43 +661,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -673,6 +721,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC06A66"/>
+      <color rgb="FFBED7EE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -682,6 +736,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -981,15 +1039,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D0B245-65CB-DF4D-8DE7-CF9F5E969E09}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.5" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="40.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" style="12" customWidth="1"/>
     <col min="7" max="7" width="48.1640625" style="6" customWidth="1"/>
     <col min="8" max="8" width="59.6640625" style="6" customWidth="1"/>
     <col min="9" max="9" width="85.5" style="7" customWidth="1"/>
@@ -1006,13 +1064,13 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1033,13 +1091,13 @@
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -1048,7 +1106,7 @@
       <c r="H2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="13" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1062,13 +1120,13 @@
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -1077,7 +1135,7 @@
       <c r="H3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="17"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -1089,13 +1147,13 @@
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -1104,7 +1162,7 @@
       <c r="H4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="17"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -1116,13 +1174,13 @@
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="6" t="s">
@@ -1131,7 +1189,7 @@
       <c r="H7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="13" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1145,13 +1203,13 @@
       <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -1160,7 +1218,7 @@
       <c r="H8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="17"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
@@ -1172,13 +1230,13 @@
       <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1187,10 +1245,10 @@
       <c r="H9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="17"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F10" s="14"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
@@ -1208,7 +1266,7 @@
       <c r="H12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="13" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1228,7 +1286,7 @@
       <c r="H13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="17"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
@@ -1246,7 +1304,7 @@
       <c r="H14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="17"/>
+      <c r="I14" s="13"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
@@ -1264,7 +1322,7 @@
       <c r="H17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="13" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1284,7 +1342,7 @@
       <c r="H18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="17"/>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
@@ -1302,59 +1360,38 @@
       <c r="H19" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="17"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>106</v>
-      </c>
+    <row r="21" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>42</v>
+      <c r="D23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>104</v>
@@ -1362,26 +1399,28 @@
       <c r="H23" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="17"/>
+      <c r="I23" s="13" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>45</v>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>104</v>
@@ -1389,62 +1428,58 @@
       <c r="H24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="17"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="27" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="A25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="28" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B28" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="J27" s="17"/>
-      <c r="K27" s="9"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>50</v>
+      <c r="D28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>108</v>
@@ -1452,28 +1487,30 @@
       <c r="H28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
+      <c r="I28" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="J28" s="13"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>54</v>
+      <c r="D29" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>108</v>
@@ -1481,60 +1518,60 @@
       <c r="H29" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
       <c r="K29" s="9"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F31" s="14"/>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="I32" s="17" t="s">
-        <v>111</v>
-      </c>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>63</v>
+      <c r="D33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>109</v>
@@ -1542,26 +1579,28 @@
       <c r="H33" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I33" s="17"/>
+      <c r="I33" s="13" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>66</v>
+      <c r="D34" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>109</v>
@@ -1569,55 +1608,56 @@
       <c r="H34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I34" s="17"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E35" s="14"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="4" t="s">
+      <c r="A35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>115</v>
-      </c>
+      <c r="C35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E36" s="11"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>72</v>
+      <c r="D38" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>116</v>
@@ -1628,22 +1668,22 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>75</v>
+      <c r="D39" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>116</v>
@@ -1652,50 +1692,50 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>113</v>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>78</v>
+      <c r="D43" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>114</v>
@@ -1706,22 +1746,22 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>84</v>
+      <c r="D44" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>114</v>
@@ -1730,50 +1770,50 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>117</v>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>93</v>
+      <c r="D48" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>87</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>126</v>
@@ -1784,22 +1824,22 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>90</v>
+      <c r="D49" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>126</v>
@@ -1809,52 +1849,52 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E50" s="14"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="A50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E51" s="11"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D53" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>157</v>
+      <c r="D53" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>125</v>
@@ -1863,276 +1903,315 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="10" t="s">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B55" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C55" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="11" t="s">
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H55" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="I54" s="12"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
+      <c r="I55" s="17"/>
+    </row>
+    <row r="56" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="17"/>
+    </row>
+    <row r="57" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="21"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B59" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C59" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D59" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E59" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F59" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G59" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H57" s="6" t="s">
+      <c r="H59" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B60" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C60" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D60" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E60" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="15" t="s">
+      <c r="F60" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G60" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="18" t="s">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="18" t="s">
+      <c r="B61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C61" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="D61" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="E61" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F59" s="19" t="s">
+      <c r="F61" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="G59" s="20" t="s">
+      <c r="G61" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H59" s="20" t="s">
+      <c r="H61" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="I59" s="21"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B64" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C64" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="D64" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E64" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="F62" s="15" t="s">
+      <c r="F64" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G64" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H62" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B65" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C65" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D65" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E65" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F63" s="15" t="s">
+      <c r="F65" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G65" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H63" s="6" t="s">
+      <c r="H65" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="18" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C66" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D66" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E66" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="F64" s="19" t="s">
+      <c r="F66" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G64" s="20" t="s">
+      <c r="G66" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H64" s="20" t="s">
+      <c r="H66" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I64" s="21"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B68" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C68" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D68" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E68" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="F66" s="15" t="s">
+      <c r="F68" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="G66" s="6" t="s">
+      <c r="G68" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H66" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B69" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C69" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D69" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E67" s="15" t="s">
+      <c r="E69" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="F67" s="15" t="s">
+      <c r="F69" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="G69" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H67" s="6" t="s">
+      <c r="H69" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="18" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B70" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C70" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D68" s="19" t="s">
+      <c r="D70" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E68" s="19" t="s">
+      <c r="E70" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="F68" s="19" t="s">
+      <c r="F70" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="G68" s="20" t="s">
+      <c r="G70" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H68" s="20" t="s">
+      <c r="H70" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="I68" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="I27:J29"/>
-    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="I33:I35"/>
+    <mergeCell ref="I28:J30"/>
+    <mergeCell ref="I23:I25"/>
     <mergeCell ref="I17:I19"/>
     <mergeCell ref="I12:I14"/>
   </mergeCells>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2140,7 +2219,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2152,7 +2231,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2164,6 +2243,312 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F1048576">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6B6AD7-F64C-7247-AEDD-F4FE3CAA8CE9}">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.1640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="20" style="12" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="47.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.83203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="42.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="21.33203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I2:I3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E1048576">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2191,6 +2576,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF923DE-FBDB-2943-875E-647209FABC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831181EC-42E3-4F42-BF23-48905B3246AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -594,7 +594,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -619,6 +619,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -670,49 +676,49 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -723,6 +729,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFE699"/>
       <color rgb="FFC06A66"/>
       <color rgb="FFBED7EE"/>
     </mruColors>
@@ -736,10 +743,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1106,7 +1109,7 @@
       <c r="H2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="22" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1135,7 +1138,7 @@
       <c r="H3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="13"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -1162,7 +1165,7 @@
       <c r="H4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="13"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -1189,7 +1192,7 @@
       <c r="H7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="22" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1218,7 +1221,7 @@
       <c r="H8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="13"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
@@ -1245,7 +1248,7 @@
       <c r="H9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="13"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F10" s="11"/>
@@ -1266,7 +1269,7 @@
       <c r="H12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="22" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1286,7 +1289,7 @@
       <c r="H13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="13"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
@@ -1304,7 +1307,7 @@
       <c r="H14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="13"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
@@ -1322,7 +1325,7 @@
       <c r="H17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="22" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1342,7 +1345,7 @@
       <c r="H18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="13"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
@@ -1360,19 +1363,19 @@
       <c r="H19" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="13"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="21"/>
+    <row r="21" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="16"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
@@ -1399,7 +1402,7 @@
       <c r="H23" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="22" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1428,7 +1431,7 @@
       <c r="H24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="13"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
@@ -1455,7 +1458,7 @@
       <c r="H25" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="13"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E26" s="11"/>
@@ -1487,10 +1490,10 @@
       <c r="H28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="J28" s="13"/>
+      <c r="J28" s="22"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -1518,8 +1521,8 @@
       <c r="H29" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
       <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -1547,8 +1550,8 @@
       <c r="H30" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
       <c r="K30" s="9"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -1579,7 +1582,7 @@
       <c r="H33" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I33" s="13" t="s">
+      <c r="I33" s="22" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1608,7 +1611,7 @@
       <c r="H34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I34" s="13"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
@@ -1635,7 +1638,7 @@
       <c r="H35" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I35" s="13"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E36" s="11"/>
@@ -1861,7 +1864,7 @@
       <c r="D50" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F50" s="12" t="s">
@@ -1929,42 +1932,30 @@
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="14" t="s">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="16" t="s">
+      <c r="G55" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I55" s="17"/>
-    </row>
-    <row r="56" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="17"/>
-    </row>
-    <row r="57" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="21"/>
+    </row>
+    <row r="57" spans="1:9" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="16"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
@@ -2132,13 +2123,13 @@
       <c r="C68" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D68" s="24" t="s">
+      <c r="D68" s="18" t="s">
         <v>152</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="F68" s="23" t="s">
+      <c r="F68" s="18" t="s">
         <v>154</v>
       </c>
       <c r="G68" s="6" t="s">
@@ -2210,6 +2201,18 @@
     <mergeCell ref="I17:I19"/>
     <mergeCell ref="I12:I14"/>
   </mergeCells>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -2270,25 +2273,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6B6AD7-F64C-7247-AEDD-F4FE3CAA8CE9}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="4" customWidth="1"/>
@@ -2330,19 +2321,19 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="21" t="s">
         <v>45</v>
       </c>
       <c r="F2" s="6" t="s">
@@ -2354,12 +2345,12 @@
       <c r="H2" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="22" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I3" s="13"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -2392,19 +2383,19 @@
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="24" t="s">
         <v>81</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2421,19 +2412,19 @@
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="27" t="s">
         <v>87</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -2450,30 +2441,18 @@
       <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="6" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
@@ -2497,37 +2476,23 @@
       <c r="G12" s="6" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I2:I3"/>
   </mergeCells>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -2576,18 +2541,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/benchmarking/search_for_best_combination/results.xlsx
+++ b/benchmarking/search_for_best_combination/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831181EC-42E3-4F42-BF23-48905B3246AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC9D729-B24F-4941-9178-7771B34C1324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{0963C398-0EAF-144E-8F53-902D2895FD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="170">
   <si>
     <t>LP HITS@10</t>
   </si>
@@ -538,6 +538,15 @@
   </si>
   <si>
     <t>NOT MORE THAN 0.20 DIFFERENCE BETWEEN LD AND LD</t>
+  </si>
+  <si>
+    <t>0.098853983</t>
+  </si>
+  <si>
+    <t>0.1402067639</t>
+  </si>
+  <si>
+    <t>0.6756550923</t>
   </si>
 </sst>
 </file>
@@ -638,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -703,15 +712,6 @@
     <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -720,6 +720,9 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1109,7 +1112,7 @@
       <c r="H2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="25" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1138,7 +1141,7 @@
       <c r="H3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -1165,7 +1168,7 @@
       <c r="H4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="22"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -1192,7 +1195,7 @@
       <c r="H7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="25" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1221,7 +1224,7 @@
       <c r="H8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="22"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
@@ -1248,7 +1251,7 @@
       <c r="H9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F10" s="11"/>
@@ -1269,7 +1272,7 @@
       <c r="H12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="25" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1289,7 +1292,7 @@
       <c r="H13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="22"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
@@ -1307,7 +1310,7 @@
       <c r="H14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="22"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
@@ -1325,7 +1328,7 @@
       <c r="H17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="25" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1345,7 +1348,7 @@
       <c r="H18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="22"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
@@ -1363,7 +1366,7 @@
       <c r="H19" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="22"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G20" s="8"/>
@@ -1402,7 +1405,7 @@
       <c r="H23" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="I23" s="25" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1431,7 +1434,7 @@
       <c r="H24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="22"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
@@ -1458,7 +1461,7 @@
       <c r="H25" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="22"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E26" s="11"/>
@@ -1490,10 +1493,10 @@
       <c r="H28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="22" t="s">
+      <c r="I28" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="J28" s="22"/>
+      <c r="J28" s="25"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -1521,8 +1524,8 @@
       <c r="H29" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
       <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -1550,8 +1553,8 @@
       <c r="H30" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
       <c r="K30" s="9"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -1582,7 +1585,7 @@
       <c r="H33" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I33" s="25" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1611,7 +1614,7 @@
       <c r="H34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I34" s="22"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
@@ -1638,7 +1641,7 @@
       <c r="H35" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I35" s="22"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E36" s="11"/>
@@ -1941,6 +1944,15 @@
       </c>
       <c r="C55" s="4" t="s">
         <v>121</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>125</v>
@@ -2279,7 +2291,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6B6AD7-F64C-7247-AEDD-F4FE3CAA8CE9}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="4" customWidth="1"/>
@@ -2345,12 +2357,12 @@
       <c r="H2" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="25" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I3" s="22"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -2383,19 +2395,19 @@
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2412,19 +2424,19 @@
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="24" t="s">
         <v>87</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -2442,38 +2454,24 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="6" t="s">
         <v>123</v>
       </c>
     </row>
